--- a/ksoft/docs/stock/Bestand_Impregnated Paper_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Impregnated Paper_Set up_details.XLSX
@@ -40814,13 +40814,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CAB64C-423B-4C7B-A24B-92FDDBA38A84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A354FCFC-1F1E-4044-AFA2-1EEAAB0CC47B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F08DE7-89C7-4D32-9EDA-749D0FF7B560}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899D6FF5-2174-4AC3-8C1E-1B2B5536BD9A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95D53903-0450-4997-AF42-2BE8E9C31EE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2741544A-57E9-472E-A28E-E362150C2751}"/>
 </file>
--- a/ksoft/docs/stock/Bestand_Impregnated Paper_Set up_details.XLSX
+++ b/ksoft/docs/stock/Bestand_Impregnated Paper_Set up_details.XLSX
@@ -40814,13 +40814,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A354FCFC-1F1E-4044-AFA2-1EEAAB0CC47B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CAB64C-423B-4C7B-A24B-92FDDBA38A84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899D6FF5-2174-4AC3-8C1E-1B2B5536BD9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F08DE7-89C7-4D32-9EDA-749D0FF7B560}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2741544A-57E9-472E-A28E-E362150C2751}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95D53903-0450-4997-AF42-2BE8E9C31EE7}"/>
 </file>